--- a/src/v2/data/Mapping onglets COREP.xlsx
+++ b/src/v2/data/Mapping onglets COREP.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maximeleyrit/Documents/COREP_CHECK/src/v2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECEDCFC-5969-5F4C-9362-2CF90119CDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BC8B98-C611-0448-9310-FFA25E6A7DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="2000" windowWidth="27640" windowHeight="16940" xr2:uid="{62770C2C-7F47-904A-A126-8F4F63279783}"/>
+    <workbookView xWindow="3180" yWindow="2000" windowWidth="27640" windowHeight="16940" activeTab="3" xr2:uid="{62770C2C-7F47-904A-A126-8F4F63279783}"/>
   </bookViews>
   <sheets>
     <sheet name="C0800" sheetId="1" r:id="rId1"/>
-    <sheet name="C0700" sheetId="2" r:id="rId2"/>
+    <sheet name="tables_mapping" sheetId="3" r:id="rId2"/>
+    <sheet name="C3300" sheetId="4" r:id="rId3"/>
+    <sheet name="formula_4_BT" sheetId="5" r:id="rId4"/>
+    <sheet name="C0700" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>New format</t>
   </si>
@@ -60,6 +63,63 @@
   </si>
   <si>
     <t>PSE-No</t>
+  </si>
+  <si>
+    <t>tables_output</t>
+  </si>
+  <si>
+    <t>tables_input</t>
+  </si>
+  <si>
+    <t>C17.01.a</t>
+  </si>
+  <si>
+    <t>C17.01.b</t>
+  </si>
+  <si>
+    <t>C16.01.a</t>
+  </si>
+  <si>
+    <t>C17.01</t>
+  </si>
+  <si>
+    <t>C16.01</t>
+  </si>
+  <si>
+    <t>formula_reference</t>
+  </si>
+  <si>
+    <t>sheet_name</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>C3300$_qx2014</t>
+  </si>
+  <si>
+    <t>qx2014</t>
+  </si>
+  <si>
+    <t>C3300$_AW</t>
+  </si>
+  <si>
+    <t>C3300$_TT</t>
+  </si>
+  <si>
+    <t>C3300$_TC</t>
+  </si>
+  <si>
+    <t>business_term</t>
+  </si>
+  <si>
+    <t>EBA:qCO(qx2000)</t>
+  </si>
+  <si>
+    <t>LEI</t>
   </si>
 </sst>
 </file>
@@ -444,6 +504,127 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007108EF-C354-D747-A426-293E3381FEEF}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99CB9D9B-9FBE-F444-B5D2-63834A86E96F}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB00E1C1-AF6F-D443-B154-DA26C1F1C01A}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F838F65C-43C2-6F48-8055-2F6E61AF3C37}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
